--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/lib-gral-bdo-o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>557639-2121-CM25</t>
+          <t>2675-56-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>13956.56</v>
+        <v>53878.44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3863-476-CM25</t>
+          <t>557639-2121-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,22 +590,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>35314.32</v>
+        <v>13956.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2776-990-CM25</t>
+          <t>3863-476-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>26632.2</v>
+        <v>35314.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2817-928-CM25</t>
+          <t>2776-990-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.090.100-5</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>50745.29</v>
+        <v>26632.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1223542-374-CM25</t>
+          <t>2817-928-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.104.928-8</t>
+          <t>69.090.100-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3283.76</v>
+        <v>50745.29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>889473-2767-CM25</t>
+          <t>1223542-374-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>65.104.928-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>20230</v>
+        <v>3283.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2777-925-CM25</t>
+          <t>889473-2767-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,22 +895,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>49673.46</v>
+        <v>20230</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3946-7-CM26</t>
+          <t>2777-925-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>18546.51</v>
+        <v>49673.46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3683-3-CM26</t>
+          <t>3946-7-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SEIDOR TECHNOLOGIES S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.449.580-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>44491.72</v>
+        <v>18546.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3946-26-CM26</t>
+          <t>3683-3-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SEIDOR TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.449.580-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1201.85</v>
+        <v>44491.72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>730736-23-CM26</t>
+          <t>3946-26-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,22 +1139,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.090.900-6</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAREDONES</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>13846.96</v>
+        <v>1201.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2675-29-CM26</t>
+          <t>730736-23-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.090.900-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE PAREDONES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>53849.29</v>
+        <v>13846.96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3838-26-CM26</t>
+          <t>2675-29-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>33023.45</v>
+        <v>53849.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2677-49-CM26</t>
+          <t>3838-26-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>37694.5</v>
+        <v>33023.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3016-71-CM26</t>
+          <t>2677-49-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,22 +1383,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.090.500-0</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOLOL</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8870.26</v>
+        <v>37694.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3764-144-CM26</t>
+          <t>3016-71-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.090.400-4</t>
+          <t>69.090.500-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NANCAGUA</t>
+          <t>I MUNICIPALIDAD DE LOLOL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6389.59</v>
+        <v>8870.26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>557639-242-CM26</t>
+          <t>3764-144-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>69.090.400-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE NANCAGUA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5072.54</v>
+        <v>6389.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1398-197-CM26</t>
+          <t>557639-242-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,32 +1591,28 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>102645.59</v>
+        <v>5072.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>522-55-CM26</t>
+          <t>1398-197-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1636,17 +1632,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.602.152-4</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,28 +1652,32 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5322.16</v>
+        <v>102645.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4732-64-CM26</t>
+          <t>522-55-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1702,12 +1702,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.602.152-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>HOSPITAL DE LITUECHE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>14192.42</v>
+        <v>5322.16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3810-279-CM26</t>
+          <t>4732-64-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9496.200000000001</v>
+        <v>14192.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1256505-27-CM26</t>
+          <t>3810-279-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1819,17 +1819,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>71.015.300-0</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1085.28</v>
+        <v>9496.200000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1622-455-CM26</t>
+          <t>1256505-27-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1870,27 +1870,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>71.015.300-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1375.64</v>
+        <v>1085.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2678-71-CM26</t>
+          <t>1622-455-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1931,27 +1931,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>79.770.640-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4878.64</v>
+        <v>1375.64</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3864-105-CM26</t>
+          <t>2678-71-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>18462.61</v>
+        <v>4878.64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>557639-614-CM26</t>
+          <t>3864-105-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1479.41</v>
+        <v>18462.61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3838-123-CM26</t>
+          <t>557639-614-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4226.88</v>
+        <v>1479.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1622-657-CM26</t>
+          <t>3838-123-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1123.87</v>
+        <v>4226.88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3863-185-CM26</t>
+          <t>1622-657-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,12 +2236,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>79.770.640-k</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7819.29</v>
+        <v>1123.87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3598-519-CM26</t>
+          <t>3863-185-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2297,27 +2297,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.091.300-3</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>16041.2</v>
+        <v>7819.29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>889473-1191-CM26</t>
+          <t>3598-519-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2363,22 +2363,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>69.091.300-3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8182.44</v>
+        <v>16041.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3996-373-CM26</t>
+          <t>889473-1191-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2424,22 +2424,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7983.23</v>
+        <v>8182.44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3731-192-CM26</t>
+          <t>3996-373-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.090.300-8</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,6 +2525,67 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
+        <v>7983.23</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3731-192-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.090.300-8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>NETSUS SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
         <v>6886.53</v>
       </c>
     </row>
